--- a/GearSage-client/rate/excel/wire_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/wire_lure_detail.xlsx
@@ -1,39 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Xiaochengxu\Diaoyoushuo\rate\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32678987-DF04-4E48-AFAB-EAF19AA94C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="5923" yWindow="2100" windowWidth="22166" windowHeight="14083" xr2:uid="{005E7AE6-BFD1-449D-BF4D-8650B74915B9}"/>
+    <workbookView windowWidth="30240" windowHeight="14640"/>
   </bookViews>
   <sheets>
-    <sheet name="hard_lure_detail" sheetId="1" r:id="rId1"/>
+    <sheet name="wire_lure_detail" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{6359F0FB-049A-4681-BB44-26B490B86F44}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -41,9 +46,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -51,15 +54,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{CE7E9198-0C4F-41F0-B589-DDAEBB67C1BD}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -67,9 +68,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -82,28 +81,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>lure_id</t>
+  </si>
+  <si>
     <t>SKU</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>lure_id</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>WEIGHT</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>sinkingspeed</t>
+  </si>
+  <si>
+    <t>referenceprice</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>COLOR</t>
+  </si>
+  <si>
+    <t>AdminCode</t>
+  </si>
+  <si>
+    <t>hook_size</t>
+  </si>
+  <si>
+    <t>depth</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>subname</t>
+  </si>
+  <si>
+    <t>other.1</t>
   </si>
   <si>
     <t>HIGH PITCHER</t>
   </si>
   <si>
     <t>1/4oz (7.0g)7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>5/16oz (9.0g)</t>
@@ -121,40 +155,219 @@
     <t>1oz (28.0g)</t>
   </si>
   <si>
-    <t>length</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>size</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>sinkingspeed</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>referenceprice</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>DLD10120</t>
+  </si>
+  <si>
+    <t>DL1013</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　マットブラック</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1,500</t>
+  </si>
+  <si>
+    <t>マットブラック</t>
+  </si>
+  <si>
+    <t>4550133578342</t>
+  </si>
+  <si>
+    <t>DLD10121</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　ブラック</t>
+  </si>
+  <si>
+    <t>ブラック</t>
+  </si>
+  <si>
+    <t>4550133578359</t>
+  </si>
+  <si>
+    <t>DLD10122</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　ホワイト</t>
+  </si>
+  <si>
+    <t>ホワイト</t>
+  </si>
+  <si>
+    <t>4550133578366</t>
+  </si>
+  <si>
+    <t>DLD10123</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　赤羽スペシャル</t>
+  </si>
+  <si>
+    <t>赤羽スペシャル</t>
+  </si>
+  <si>
+    <t>4550133578373</t>
+  </si>
+  <si>
+    <t>DLD10124</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　クロキン</t>
+  </si>
+  <si>
+    <t>クロキン</t>
+  </si>
+  <si>
+    <t>4550133578380</t>
+  </si>
+  <si>
+    <t>DLD10125</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　ワカサギ</t>
+  </si>
+  <si>
+    <t>ワカサギ</t>
+  </si>
+  <si>
+    <t>4550133578397</t>
+  </si>
+  <si>
+    <t>DLD10126</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　キタサンホワイト</t>
+  </si>
+  <si>
+    <t>キタサンホワイト</t>
+  </si>
+  <si>
+    <t>4550133578403</t>
+  </si>
+  <si>
+    <t>DLD10127</t>
+  </si>
+  <si>
+    <t>ＳＴＥＥＺバズベイト１／２ｏｚ　ライムチャート</t>
+  </si>
+  <si>
+    <t>ライムチャート</t>
+  </si>
+  <si>
+    <t>4550133578410</t>
+  </si>
+  <si>
+    <t>DLD10231</t>
+  </si>
+  <si>
+    <t>DL1026</t>
+  </si>
+  <si>
+    <t>1/4oz TW</t>
+  </si>
+  <si>
+    <t>タンデムウィロー</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>DLD10232</t>
+  </si>
+  <si>
+    <t>1/4oz DW</t>
+  </si>
+  <si>
+    <t>ダブルウィロー</t>
+  </si>
+  <si>
+    <t>DW</t>
+  </si>
+  <si>
+    <t>DLD10233</t>
+  </si>
+  <si>
+    <t>3/8oz TW</t>
+  </si>
+  <si>
+    <t>DLD10234</t>
+  </si>
+  <si>
+    <t>3/8oz DW</t>
+  </si>
+  <si>
+    <t>DLD10235</t>
+  </si>
+  <si>
+    <t>1/2oz TW</t>
+  </si>
+  <si>
+    <t>DLD10236</t>
+  </si>
+  <si>
+    <t>1/2oz DW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -162,16 +375,22 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -180,7 +399,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -189,31 +407,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -221,7 +414,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -230,7 +422,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -239,15 +430,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -256,24 +438,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +453,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -290,44 +481,19 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="6"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="PingFang SC"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -339,175 +505,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -517,6 +696,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -542,7 +736,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,15 +771,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -601,17 +786,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,203 +806,228 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -872,7 +1076,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -905,26 +1109,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -957,23 +1144,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1115,52 +1285,74 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D8A09D-4FE5-4991-A669-888E908873A1}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="3" max="3" width="13.640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.0703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6428571428571" customWidth="1"/>
+    <col min="4" max="4" width="12.0714285714286" customWidth="1"/>
+    <col min="7" max="7" width="11.6428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="17.6" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1168,15 +1360,15 @@
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1184,15 +1376,15 @@
         <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1200,15 +1392,15 @@
         <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1216,15 +1408,15 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1232,15 +1424,15 @@
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1248,16 +1440,590 @@
         <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="17.6" spans="1:17">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="17.6" spans="1:17">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="17.6" spans="1:17">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="17.6" spans="1:17">
+      <c r="A11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="17.6" spans="1:17">
+      <c r="A12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="17.6" spans="1:17">
+      <c r="A13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="17.6" spans="1:17">
+      <c r="A14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="17.6" spans="1:17">
+      <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="17.6" spans="1:17">
+      <c r="A16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="17.6" spans="1:13">
+      <c r="A17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="17.6" spans="1:13">
+      <c r="A18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="17.6" spans="1:13">
+      <c r="A19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="17.6" spans="1:13">
+      <c r="A20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="17.6" spans="1:13">
+      <c r="A21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/wire_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/wire_lure_detail.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -453,11 +457,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>11</v>
+      <c r="A2" t="str">
+        <v>OSPD10000</v>
+      </c>
+      <c r="B2" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="C2" t="str">
         <v>HIGH PITCHER</v>
@@ -506,11 +510,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>11</v>
+      <c r="A3" t="str">
+        <v>OSPD10001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="C3" t="str">
         <v>HIGH PITCHER</v>
@@ -559,11 +563,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
+      <c r="A4" t="str">
+        <v>OSPD10002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="C4" t="str">
         <v>HIGH PITCHER</v>
@@ -612,11 +616,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
+      <c r="A5" t="str">
+        <v>OSPD10003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="C5" t="str">
         <v>HIGH PITCHER</v>
@@ -665,11 +669,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>11</v>
+      <c r="A6" t="str">
+        <v>OSPD10004</v>
+      </c>
+      <c r="B6" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="C6" t="str">
         <v>HIGH PITCHER</v>
@@ -718,11 +722,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
+      <c r="A7" t="str">
+        <v>OSPD10005</v>
+      </c>
+      <c r="B7" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="C7" t="str">
         <v>HIGH PITCHER</v>
@@ -810,6 +814,18 @@
       <c r="M8" t="str">
         <v/>
       </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -851,6 +867,18 @@
       <c r="M9" t="str">
         <v/>
       </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -892,6 +920,18 @@
       <c r="M10" t="str">
         <v/>
       </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -933,6 +973,18 @@
       <c r="M11" t="str">
         <v/>
       </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -974,6 +1026,18 @@
       <c r="M12" t="str">
         <v/>
       </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1015,6 +1079,18 @@
       <c r="M13" t="str">
         <v/>
       </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1056,6 +1132,18 @@
       <c r="M14" t="str">
         <v/>
       </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1097,6 +1185,18 @@
       <c r="M15" t="str">
         <v/>
       </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1138,6 +1238,18 @@
       <c r="M16" t="str">
         <v/>
       </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1179,6 +1291,18 @@
       <c r="M17" t="str">
         <v/>
       </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1220,6 +1344,18 @@
       <c r="M18" t="str">
         <v/>
       </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1261,6 +1397,18 @@
       <c r="M19" t="str">
         <v/>
       </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1302,6 +1450,18 @@
       <c r="M20" t="str">
         <v/>
       </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1341,6 +1501,18 @@
         <v/>
       </c>
       <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
         <v/>
       </c>
     </row>

--- a/GearSage-client/rate/excel/wire_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/wire_lure_detail.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">

--- a/GearSage-client/rate/excel/wire_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/wire_lure_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1512,9 +1512,168 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>KLD10020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>KL1020</v>
+      </c>
+      <c r="C22" t="str">
+        <v>TEEボーンバズベイト</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>2026-04-10T05:01:36.834Z</v>
+      </c>
+      <c r="J22" t="str">
+        <v>2026-04-10T05:01:36.834Z</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>KLD10021</v>
+      </c>
+      <c r="B23" t="str">
+        <v>KL1021</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ベイビーTEE-BONE スピナーベイト</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>2026-04-10T05:01:39.158Z</v>
+      </c>
+      <c r="J23" t="str">
+        <v>2026-04-10T05:01:39.158Z</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>KLD10022</v>
+      </c>
+      <c r="B24" t="str">
+        <v>KL1022</v>
+      </c>
+      <c r="C24" t="str">
+        <v>TEE-BONE スピナーベイト</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>2026-04-10T05:01:40.855Z</v>
+      </c>
+      <c r="J24" t="str">
+        <v>2026-04-10T05:01:40.855Z</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/wire_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/wire_lure_detail.xlsx
@@ -1514,7 +1514,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>KLD10020</v>
+        <v>KLD10070</v>
       </c>
       <c r="B22" t="str">
         <v>KL1020</v>
@@ -1538,10 +1538,10 @@
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>KLD10021</v>
+        <v>KLD10071</v>
       </c>
       <c r="B23" t="str">
         <v>KL1021</v>
       </c>
       <c r="C23" t="str">
-        <v>ベイビーTEE-BONE スピナーベイト</v>
+        <v>ウエイトは3サイズで展開</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>1/2oz</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>ウエイトは3サイズで展開</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1591,10 +1591,10 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>KLD10022</v>
+        <v>KLD10072</v>
       </c>
       <c r="B24" t="str">
         <v>KL1022</v>
@@ -1644,10 +1644,10 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="K24" t="str">
         <v/>
